--- a/TP2026/MiniProjets.xlsx
+++ b/TP2026/MiniProjets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tahto\OneDrive\Documents\GitHub\u3\TP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791FD15E-79FC-47BE-839E-AFB768C147EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0454C8-01DE-450C-913C-E6ACE0791E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="607" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="607" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proj 1 - Epicerie" sheetId="2" r:id="rId1"/>
@@ -689,71 +689,71 @@
     <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1032,70 +1032,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
     </row>
     <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -1233,43 +1233,43 @@
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
       <c r="G16" s="8"/>
     </row>
     <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
       <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
       <c r="G18" s="8"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
       <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1284,29 +1284,29 @@
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1328,70 +1328,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
     </row>
     <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -1514,43 +1514,43 @@
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="12"/>
     </row>
     <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
       <c r="G16" s="12"/>
     </row>
     <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
       <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1565,29 +1565,29 @@
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1609,70 +1609,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
     </row>
     <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -1805,43 +1805,43 @@
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
       <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
       <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1856,29 +1856,29 @@
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1899,70 +1899,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -2124,33 +2124,33 @@
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
       <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
       <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
       <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2165,28 +2165,28 @@
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B20:H20"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B20:H20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2206,70 +2206,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
     </row>
     <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -2385,43 +2385,43 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
       <c r="G14" s="24"/>
     </row>
     <row r="15" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
       <c r="G15" s="24"/>
     </row>
     <row r="16" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
       <c r="G16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
       <c r="G17" s="24"/>
     </row>
     <row r="18" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2436,29 +2436,29 @@
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
